--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0199.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0199.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Và... giờ khi ta về nhà, bố mẹ ta đã ở đó.</t>
+          <t>Và... giờ khi tao về nhà, bố mẹ tao đã ở đó.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Họ đã ở đây, chờ đợi ta suốt thời gian qua. Và giờ, cuối cùng ta cũng được ở bên họ.</t>
+          <t>Họ đã ở đây, chờ đợi tao suốt thời gian qua. Và giờ, cuối cùng tao cũng được ở bên họ.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Nếu sau này chúng ta cùng lớp, nhớ tìm ta nhé. Chắc sẽ vui lắm.</t>
+          <t>Nếu sau này chúng ta cùng lớp, nhớ tìm tao nhé. Chắc sẽ vui lắm.</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Ta nghĩ nó đại diện cho một sức mạnh... hoàn toàn khác với nỗi sợ hãi.</t>
+          <t>Tao nghĩ nó đại diện cho một sức mạnh... hoàn toàn khác với nỗi sợ hãi.</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Ta đã hứa với Augusta là khi mọi chuyện ổn định, ta sẽ đến Thành phố Septimont.</t>
+          <t>Tao đã hứa với Augusta là khi mọi chuyện ổn định, tao sẽ đến Thành phố Septimont.</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Vậy là giờ ta lại lang thang ngoài đường một mình thế này.</t>
+          <t>Vậy là giờ tao lại lang thang ngoài đường một mình thế này.</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Hê, ta hiểu gánh nặng trách nhiệm của ngươi lắm. Nhưng hãy lo cho bản thân trước khi lo cho người khác nhé.</t>
+          <t>Hê, tao hiểu gánh nặng trách nhiệm của mày lắm. Nhưng hãy lo cho bản thân trước khi lo cho người khác nhé.</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Hôm nay có việc gì mà cậu lại đến dinh thự thế?</t>
+          <t>Hôm nay có việc gì mà bạn lại đến dinh thự thế?</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Quyết định thế nhé. Tối nay, tại đấu trường Titanbone Expanse. Ta sẽ có mặt.</t>
+          <t>Quyết định thế nhé. Tối nay, tại đấu trường Titanbone Expanse. Tao sẽ có mặt.</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Lần đầu ta đứng đây, ta chỉ là một đấu sĩ vô danh. Ta thường lẻn vào sau khi trời tối, khi đám đông đã tan và thành phố chìm vào giấc ngủ.</t>
+          <t>Lần đầu tao đứng đây, tao chỉ là một đấu sĩ vô danh. Tao thường lẻn vào sau khi trời tối, khi đám đông đã tan và thành phố chìm vào giấc ngủ.</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Ta cũng tin vậy.</t>
+          <t>Tao cũng tin vậy.</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Ừm... Ta quên mất mình có thể đa cảm đến thế nào khi cuối cùng cũng cho phép bản thân thư giãn.</t>
+          <t>Ừm... Tao quên mất mình có thể đa cảm đến thế nào khi cuối cùng cũng cho phép bản thân thư giãn.</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Được rồi. Ta sẽ nói cho ngươi biết.</t>
+          <t>Được rồi. Tao sẽ nói cho mày biết.</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Ừm... Ta quên mất mình có thể đa cảm đến thế nào khi cuối cùng cũng cho phép bản thân thư giãn.</t>
+          <t>Ừm... Tao quên mất mình có thể đa cảm đến thế nào khi cuối cùng cũng cho phép bản thân thư giãn.</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Được rồi. Ta sẽ nói cho ngươi biết.</t>
+          <t>Được rồi. Tao sẽ nói cho mày biết.</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Ta đã có linh cảm sẽ gặp ngươi ở đây.</t>
+          <t>Tao đã có linh cảm sẽ gặp mày ở đây.</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Chỉ có mình ta gọi ngươi như thế thôi, nên... chịu đi! Ngươi đành phải cắn răng chịu đựng thôi, phải không?</t>
+          <t>Chỉ có mình tao gọi mày như thế thôi, nên... chịu đi! Mày đành phải cắn răng chịu đựng thôi, phải không?</t>
         </is>
       </c>
     </row>
@@ -24819,7 +24819,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Nhưng ta vốn ghét luật lệ. Cái trật tự ấy, sự phục tùng nhàm chán ấy... ngột ngạt quá. Nên mỗi khi cảm thấy ngộp thở, ta lại đến đây. Để ngắm trăng.</t>
+          <t>Nhưng tao vốn ghét luật lệ. Cái trật tự ấy, sự phục tùng nhàm chán ấy... ngột ngạt quá. Nên mỗi khi cảm thấy ngộp thở, tao lại đến đây. Để ngắm trăng.</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Ở đây có nhiều hơn một mặt trăng. Một cái trên trời... và một cái dưới nước. Nói ta nghe, cái nào khó chạm tới hơn?</t>
+          <t>Ở đây có nhiều hơn một mặt trăng. Một cái trên trời... và một cái dưới nước. Nói tao nghe, cái nào khó chạm tới hơn?</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Không thể làm khác được. Ta &lt;i&gt;đúng là&lt;/i&gt; thiên tài mà. Không chịu thua là bản chất... thắng cũng vậy thôi.</t>
+          <t>Không thể làm khác được. Tao &lt;i&gt;đúng là&lt;/i&gt; thiên tài mà. Không chịu thua là bản chất... thắng cũng vậy thôi.</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Ta đã bảo rồi, ta rất hào phóng mà. Đặc biệt là với ngươi. Một món quà thôi à? Haha, thế thì chưa đủ đâu.</t>
+          <t>Tao đã bảo rồi, tao rất hào phóng mà. Đặc biệt là với mày. Một món quà thôi à? Haha, thế thì chưa đủ đâu.</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Ủa? Chỉ vì ta thích nên ngươi mới có mặt ở đây thôi hả?</t>
+          <t>Ủa? Chỉ vì tao thích nên mày mới có mặt ở đây thôi hả?</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Thường thì ta thích những cuộc gặp bất ngờ. Nhưng với ngươi... kể cả cuộc hẹn có lên kế hoạch trước, vẫn vui bất ngờ.</t>
+          <t>Thường thì tao thích những cuộc gặp bất ngờ. Nhưng với mày... kể cả cuộc hẹn có lên kế hoạch trước, vẫn vui bất ngờ.</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Đừng nhìn ta như thế... Được rồi, được rồi! Dù ta có đi đâu, ta cũng sẽ báo cho ngươi biết chỗ ở.</t>
+          <t>Đừng nhìn tao như thế... Được rồi, được rồi! Dù tao có đi đâu, tao cũng sẽ báo cho mày biết chỗ ở.</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Mỗi lần ngắm biển… ta lại thấy lòng vui lạ thường.</t>
+          <t>Mỗi lần ngắm biển… tao lại thấy lòng vui lạ thường.</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Nhưng ta không thể luôn ở đây được. Là một Người Mang Hoa, ta có trách nhiệm của riêng mình.</t>
+          <t>Nhưng tao không thể luôn ở đây được. Là một Người Mang Hoa, tao có trách nhiệm của riêng mình.</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Ôi… ta á? Nhưng kẻ đứng sau tấm màn đâu có được bước lên sân khấu đâu.</t>
+          <t>Ôi… tao á? Nhưng kẻ đứng sau tấm màn đâu có được bước lên sân khấu đâu.</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Xin chào, {PlayerName}.</t>
+          <t>Chào {PlayerName}.</t>
         </is>
       </c>
     </row>
